--- a/stories/arbres/TREE-EMO-018.xlsx
+++ b/stories/arbres/TREE-EMO-018.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est au bord de la mer avec papa. Le jeu devient trop fort. Le vent pousse le sable. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte. Maman est sur la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom reste un moment avec un copain qui s'appelle Tom aussi. Une feuille tombe. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Le soleil chauffe un peu. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Le sol est frais. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3943,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4110,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Le sol est frais. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4277,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4444,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Un petit bruit d'eau. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4611,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4778,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4945,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5112,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5303,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5470,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5637,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5804,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5971,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6138,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6305,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6472,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Léa. Le vent est doux. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6653,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6826,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7017,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7184,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7375,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7542,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Le sol est frais. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7709,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7876,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8043,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8210,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Les chaussures font toc toc. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8377,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8544,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8735,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8902,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9069,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9236,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9403,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9570,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9737,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9904,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10095,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10262,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Les chaussures font toc toc. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10429,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10596,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10763,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10930,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. La lumière est claire. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11097,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11264,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Sami. On entend un oiseau. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11445,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11618,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11809,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11649,6 +11976,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12167,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12334,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12501,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12668,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12835,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13002,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13169,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13336,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13527,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13694,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13861,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14028,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. Un vélo passe au loin. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14195,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14362,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. La lumière est claire. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14529,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14696,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14887,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15054,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend une pomme, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15221,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15388,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un yaourt, près de papa. La lumière est claire. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15555,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15722,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend un morceau de pain, près de papa. Ça sent le pain. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15889,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15929,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-018.xlsx
+++ b/stories/arbres/TREE-EMO-018.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Tom est au bord de la mer avec papa. Le jeu devient trop fort. Le vent pousse le sable. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte. Maman est sur la serviette.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Tom reste un moment avec un copain qui s'appelle Tom aussi. Une feuille tombe. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Le soleil chauffe un peu. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Le sol est frais. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3948,6 +3968,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4115,6 +4136,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Le sol est frais. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4282,6 +4304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4449,6 +4472,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Un petit bruit d'eau. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4616,6 +4640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4783,6 +4808,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4950,6 +4976,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5117,6 +5144,7 @@
           <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5308,6 +5336,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5475,6 +5504,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5642,6 +5672,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5809,6 +5840,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5976,6 +6008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6143,6 +6176,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6310,6 +6344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6477,6 +6512,7 @@
           <t>narrateur|Tom rejoint Léa. Le vent est doux. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6660,6 +6696,7 @@
           <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6831,6 +6868,7 @@
           <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7022,6 +7060,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7189,6 +7228,7 @@
           <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7380,6 +7420,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7547,6 +7588,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Le sol est frais. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7714,6 +7756,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7881,6 +7924,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8048,6 +8092,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8215,6 +8260,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Les chaussures font toc toc. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8382,6 +8428,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8549,6 +8596,7 @@
           <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8740,6 +8788,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8907,6 +8956,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9074,6 +9124,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9241,6 +9292,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9408,6 +9460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9575,6 +9628,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9742,6 +9796,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9909,6 +9964,7 @@
           <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10100,6 +10156,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10267,6 +10324,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Les chaussures font toc toc. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10434,6 +10492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10601,6 +10660,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10768,6 +10828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10935,6 +10996,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. La lumière est claire. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11102,6 +11164,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11269,6 +11332,7 @@
           <t>narrateur|Tom rejoint Sami. On entend un oiseau. C'est trop près, trop fort. Tom dit stop. Tom s'éloigne. Tom va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11452,6 +11516,7 @@
           <t>narrateur|Le jeu est trop fort. Tom fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11623,6 +11688,7 @@
           <t>narrateur|Oui. Stop. Tom s'éloigne. Vers papa, l'adulte. On continue.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11814,6 +11880,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11981,6 +12048,7 @@
           <t>narrateur|Le jeu était vers le bac à sable. Ça sent l'herbe coupée. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12172,6 +12240,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12339,6 +12408,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Un petit bruit d'eau. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12506,6 +12576,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12673,6 +12744,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Les chaussures font toc toc. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12840,6 +12912,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13007,6 +13080,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Un vélo passe au loin. Après le bac à sable, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13174,6 +13248,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13341,6 +13416,7 @@
           <t>narrateur|Le jeu était vers le toboggan. Le soleil chauffe un peu. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13532,6 +13608,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13699,6 +13776,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Les chaussures font toc toc. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13866,6 +13944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14033,6 +14112,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. Un vélo passe au loin. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14200,6 +14280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14367,6 +14448,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. La lumière est claire. Après le toboggan, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14534,6 +14616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14701,6 +14784,7 @@
           <t>narrateur|Le jeu était vers les balançoires. Le sol est frais. Encore trop fort. Tom dit stop. Tom s'éloigne. Papa, l'adulte, ouvre les bras. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14892,6 +14976,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15059,6 +15144,7 @@
           <t>narrateur|Tom prend une pomme, près de papa. Un vélo passe au loin. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15226,6 +15312,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15393,6 +15480,7 @@
           <t>narrateur|Tom prend un yaourt, près de papa. La lumière est claire. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15560,6 +15648,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15727,6 +15816,7 @@
           <t>narrateur|Tom prend un morceau de pain, près de papa. Ça sent le pain. Après les balançoires, Tom a dit stop. Tom s'est éloigné. Vers papa, l'adulte. Merci papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15894,6 +15984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15912,7 +16003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15936,6 +16027,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15950,7 +16055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16137,6 +16242,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
